--- a/data/WP18_beteiligte_ministerien.xlsx
+++ b/data/WP18_beteiligte_ministerien.xlsx
@@ -377,55 +377,67 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>6369</v>
+        <v>3636</v>
       </c>
       <c r="C2" t="n">
-        <v>33.1286926461346</v>
-      </c>
-      <c r="D2"/>
-      <c r="E2"/>
+        <v>35.3454345434542</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2578</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29.0979097909791</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4323</v>
+        <v>2433</v>
       </c>
       <c r="C3" t="n">
-        <v>34.1433202130123</v>
-      </c>
-      <c r="D3"/>
-      <c r="E3"/>
+        <v>35.67283189478</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1877</v>
+      </c>
+      <c r="E3" t="n">
+        <v>22.852445540485</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2257</v>
+        <v>942</v>
       </c>
       <c r="C4" t="n">
-        <v>33.5037694013305</v>
-      </c>
-      <c r="D4"/>
-      <c r="E4"/>
+        <v>38.2441613588111</v>
+      </c>
+      <c r="D4" t="n">
+        <v>804</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14.6496815286624</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>707</v>
+        <v>277</v>
       </c>
       <c r="C5" t="n">
-        <v>35.7920792079208</v>
+        <v>37.8447653429603</v>
       </c>
       <c r="D5" t="n">
-        <v>577</v>
+        <v>245</v>
       </c>
       <c r="E5" t="n">
-        <v>18.3875530410184</v>
+        <v>11.5523465703971</v>
       </c>
     </row>
     <row r="6">
@@ -433,16 +445,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="C6" t="n">
-        <v>38.0674157303371</v>
+        <v>37.0869565217391</v>
       </c>
       <c r="D6" t="n">
-        <v>153</v>
+        <v>41</v>
       </c>
       <c r="E6" t="n">
-        <v>14.0449438202247</v>
+        <v>10.8695652173913</v>
       </c>
     </row>
     <row r="7">
@@ -450,50 +462,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>36.4782608695652</v>
+        <v>35.5714285714286</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>4.34782608695652</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C8" t="n">
-        <v>41.4444444444444</v>
-      </c>
-      <c r="D8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -730,13 +708,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A869DBAF-984C-4086-9C5D-92A827A58AC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F803228B-D89E-4A6F-A92E-784676E5A8DB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F544E74C-FCCF-4C59-8268-898431AD214C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5C48AA7-DC5F-49B2-A0DF-375A8D198EC8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CFDB2B-4F5C-4F77-8B09-84E67C8F0BF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D536453-3C35-4700-AFF4-ADE1B4EDBE7D}"/>
 </file>